--- a/artfynd/A 59039-2024 artfynd.xlsx
+++ b/artfynd/A 59039-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118578481</v>
+        <v>118578478</v>
       </c>
       <c r="B2" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>522009</v>
+        <v>522048</v>
       </c>
       <c r="R2" t="n">
-        <v>7207890</v>
+        <v>7207921</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118578470</v>
+        <v>118578473</v>
       </c>
       <c r="B3" t="n">
-        <v>90527</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521972</v>
+        <v>521735</v>
       </c>
       <c r="R3" t="n">
-        <v>7207877</v>
+        <v>7207744</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,59 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118578467</v>
+        <v>118578495</v>
       </c>
       <c r="B4" t="n">
-        <v>57403</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Råmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522040</v>
+        <v>521714</v>
       </c>
       <c r="R4" t="n">
-        <v>7207921</v>
+        <v>7208121</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118578498</v>
+        <v>118578461</v>
       </c>
       <c r="B5" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>522045</v>
+        <v>521597</v>
       </c>
       <c r="R5" t="n">
-        <v>7207939</v>
+        <v>7208138</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118578487</v>
+        <v>118578464</v>
       </c>
       <c r="B6" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521645</v>
+        <v>521674</v>
       </c>
       <c r="R6" t="n">
-        <v>7207715</v>
+        <v>7208184</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118578492</v>
+        <v>118578474</v>
       </c>
       <c r="B7" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1210,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>521645</v>
+        <v>521672</v>
       </c>
       <c r="R7" t="n">
-        <v>7208166</v>
+        <v>7207724</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118578468</v>
+        <v>118578482</v>
       </c>
       <c r="B8" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>522032</v>
+        <v>521978</v>
       </c>
       <c r="R8" t="n">
-        <v>7207899</v>
+        <v>7207864</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118578463</v>
+        <v>118578484</v>
       </c>
       <c r="B9" t="n">
-        <v>82272</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1414,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521618</v>
+        <v>521730</v>
       </c>
       <c r="R9" t="n">
-        <v>7208151</v>
+        <v>7207763</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118578494</v>
+        <v>118578486</v>
       </c>
       <c r="B10" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521680</v>
+        <v>521694</v>
       </c>
       <c r="R10" t="n">
-        <v>7208186</v>
+        <v>7207714</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118578497</v>
+        <v>118578488</v>
       </c>
       <c r="B11" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1618,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>522032</v>
+        <v>521602</v>
       </c>
       <c r="R11" t="n">
-        <v>7208002</v>
+        <v>7207698</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118578465</v>
+        <v>118578499</v>
       </c>
       <c r="B12" t="n">
-        <v>90527</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1720,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>521721</v>
+        <v>522039</v>
       </c>
       <c r="R12" t="n">
-        <v>7208199</v>
+        <v>7208000</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118578491</v>
+        <v>118578468</v>
       </c>
       <c r="B13" t="n">
-        <v>90527</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1822,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521615</v>
+        <v>522032</v>
       </c>
       <c r="R13" t="n">
-        <v>7208150</v>
+        <v>7207899</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118578464</v>
+        <v>118578490</v>
       </c>
       <c r="B14" t="n">
-        <v>90509</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1924,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521674</v>
+        <v>521591</v>
       </c>
       <c r="R14" t="n">
-        <v>7208184</v>
+        <v>7208143</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,37 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118578478</v>
+        <v>118578465</v>
       </c>
       <c r="B15" t="n">
-        <v>77440</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>314</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>522048</v>
+        <v>521721</v>
       </c>
       <c r="R15" t="n">
-        <v>7207921</v>
+        <v>7208199</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,37 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118578471</v>
+        <v>118578470</v>
       </c>
       <c r="B16" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>521954</v>
+        <v>521972</v>
       </c>
       <c r="R16" t="n">
-        <v>7207893</v>
+        <v>7207877</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,37 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118578461</v>
+        <v>118578491</v>
       </c>
       <c r="B17" t="n">
-        <v>90509</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>521597</v>
+        <v>521615</v>
       </c>
       <c r="R17" t="n">
-        <v>7208138</v>
+        <v>7208150</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2316,37 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118578489</v>
+        <v>118578463</v>
       </c>
       <c r="B18" t="n">
-        <v>97879</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2356,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>521552</v>
+        <v>521618</v>
       </c>
       <c r="R18" t="n">
-        <v>7208141</v>
+        <v>7208151</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,15 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118578482</v>
+        <v>118578500</v>
       </c>
       <c r="B19" t="n">
-        <v>90509</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2434,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2458,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>521978</v>
+        <v>522033</v>
       </c>
       <c r="R19" t="n">
-        <v>7207864</v>
+        <v>7207961</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2520,37 +2421,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118578500</v>
+        <v>118578476</v>
       </c>
       <c r="B20" t="n">
-        <v>82272</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2560,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>522033</v>
+        <v>521569</v>
       </c>
       <c r="R20" t="n">
-        <v>7207961</v>
+        <v>7207723</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2622,37 +2518,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118578486</v>
+        <v>118578458</v>
       </c>
       <c r="B21" t="n">
-        <v>90509</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2662,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>521694</v>
+        <v>521536</v>
       </c>
       <c r="R21" t="n">
-        <v>7207714</v>
+        <v>7207640</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2724,37 +2615,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118578473</v>
+        <v>118578460</v>
       </c>
       <c r="B22" t="n">
-        <v>90797</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2764,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>521735</v>
+        <v>521562</v>
       </c>
       <c r="R22" t="n">
-        <v>7207744</v>
+        <v>7208148</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2826,37 +2712,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118578488</v>
+        <v>118578466</v>
       </c>
       <c r="B23" t="n">
-        <v>90509</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2866,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>521602</v>
+        <v>521789</v>
       </c>
       <c r="R23" t="n">
-        <v>7207698</v>
+        <v>7207952</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2928,19 +2809,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118578466</v>
+        <v>118578471</v>
       </c>
       <c r="B24" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2968,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>521789</v>
+        <v>521954</v>
       </c>
       <c r="R24" t="n">
-        <v>7207952</v>
+        <v>7207893</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3030,37 +2906,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118578479</v>
+        <v>118578472</v>
       </c>
       <c r="B25" t="n">
-        <v>74605</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3070,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>522044</v>
+        <v>521737</v>
       </c>
       <c r="R25" t="n">
-        <v>7207901</v>
+        <v>7207804</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3132,37 +3003,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118578474</v>
+        <v>118578481</v>
       </c>
       <c r="B26" t="n">
-        <v>90509</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3172,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>521672</v>
+        <v>522009</v>
       </c>
       <c r="R26" t="n">
-        <v>7207724</v>
+        <v>7207890</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3234,37 +3100,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118578496</v>
+        <v>118578487</v>
       </c>
       <c r="B27" t="n">
-        <v>97879</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3274,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>521819</v>
+        <v>521645</v>
       </c>
       <c r="R27" t="n">
-        <v>7207968</v>
+        <v>7207715</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3336,37 +3197,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118578484</v>
+        <v>118578492</v>
       </c>
       <c r="B28" t="n">
-        <v>90509</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521730</v>
+        <v>521645</v>
       </c>
       <c r="R28" t="n">
-        <v>7207763</v>
+        <v>7208166</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,19 +3294,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118578460</v>
+        <v>118578497</v>
       </c>
       <c r="B29" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3478,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521562</v>
+        <v>522032</v>
       </c>
       <c r="R29" t="n">
-        <v>7208148</v>
+        <v>7208002</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3540,15 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118578490</v>
+        <v>118578479</v>
       </c>
       <c r="B30" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3556,21 +3402,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3580,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521591</v>
+        <v>522044</v>
       </c>
       <c r="R30" t="n">
-        <v>7208143</v>
+        <v>7207901</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3642,15 +3488,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118578475</v>
+        <v>118578467</v>
       </c>
       <c r="B31" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3658,34 +3499,43 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Råmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>521625</v>
+        <v>522040</v>
       </c>
       <c r="R31" t="n">
-        <v>7207718</v>
+        <v>7207921</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3744,15 +3594,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118578476</v>
+        <v>118578489</v>
       </c>
       <c r="B32" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3760,21 +3605,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3784,10 +3629,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521569</v>
+        <v>521552</v>
       </c>
       <c r="R32" t="n">
-        <v>7207723</v>
+        <v>7208141</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3846,37 +3691,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118578499</v>
+        <v>118578496</v>
       </c>
       <c r="B33" t="n">
-        <v>90509</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3886,10 +3726,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>522039</v>
+        <v>521819</v>
       </c>
       <c r="R33" t="n">
-        <v>7208000</v>
+        <v>7207968</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3945,108 +3785,6 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>118578472</v>
-      </c>
-      <c r="B34" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Råmyran, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>521737</v>
-      </c>
-      <c r="R34" t="n">
-        <v>7207804</v>
-      </c>
-      <c r="S34" t="n">
-        <v>10</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AD34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>Elias Forsberg</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>Elias Forsberg</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
